--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641539</v>
+        <v>121641537</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>98017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429471</v>
+        <v>429401</v>
       </c>
       <c r="R3" t="n">
-        <v>6383434</v>
+        <v>6383436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Ellen Hultman, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641537</v>
+        <v>121641538</v>
       </c>
       <c r="B4" t="n">
         <v>98017</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429401</v>
+        <v>429422</v>
       </c>
       <c r="R4" t="n">
-        <v>6383436</v>
+        <v>6383435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641538</v>
+        <v>121641539</v>
       </c>
       <c r="B5" t="n">
-        <v>98017</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429422</v>
+        <v>429471</v>
       </c>
       <c r="R5" t="n">
-        <v>6383435</v>
+        <v>6383434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Anna Ljungqvist</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641540</v>
+        <v>121641538</v>
       </c>
       <c r="B2" t="n">
-        <v>91133</v>
+        <v>98017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429450</v>
+        <v>429422</v>
       </c>
       <c r="R2" t="n">
-        <v>6383433</v>
+        <v>6383435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Ellen Hultman, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641537</v>
+        <v>121641539</v>
       </c>
       <c r="B3" t="n">
-        <v>98017</v>
+        <v>5173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429401</v>
+        <v>429471</v>
       </c>
       <c r="R3" t="n">
-        <v>6383436</v>
+        <v>6383434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Anna Ljungqvist</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641538</v>
+        <v>121641537</v>
       </c>
       <c r="B4" t="n">
         <v>98017</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429422</v>
+        <v>429401</v>
       </c>
       <c r="R4" t="n">
-        <v>6383435</v>
+        <v>6383436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641539</v>
+        <v>121641540</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>91133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429471</v>
+        <v>429450</v>
       </c>
       <c r="R5" t="n">
-        <v>6383434</v>
+        <v>6383433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641537</v>
+        <v>121641540</v>
       </c>
       <c r="B4" t="n">
-        <v>98017</v>
+        <v>91133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429401</v>
+        <v>429450</v>
       </c>
       <c r="R4" t="n">
-        <v>6383436</v>
+        <v>6383433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Anna Ljungqvist</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641540</v>
+        <v>121641537</v>
       </c>
       <c r="B5" t="n">
-        <v>91133</v>
+        <v>98017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429450</v>
+        <v>429401</v>
       </c>
       <c r="R5" t="n">
-        <v>6383433</v>
+        <v>6383436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Ellen Hultman, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641538</v>
+        <v>121641540</v>
       </c>
       <c r="B2" t="n">
-        <v>98017</v>
+        <v>91133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429422</v>
+        <v>429450</v>
       </c>
       <c r="R2" t="n">
-        <v>6383435</v>
+        <v>6383433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Anna Ljungqvist</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641539</v>
+        <v>121641538</v>
       </c>
       <c r="B3" t="n">
-        <v>5173</v>
+        <v>98017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>220093</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429471</v>
+        <v>429422</v>
       </c>
       <c r="R3" t="n">
-        <v>6383434</v>
+        <v>6383435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Ellen Hultman, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641540</v>
+        <v>121641537</v>
       </c>
       <c r="B4" t="n">
-        <v>91133</v>
+        <v>98017</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429450</v>
+        <v>429401</v>
       </c>
       <c r="R4" t="n">
-        <v>6383433</v>
+        <v>6383436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Ellen Hultman, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641537</v>
+        <v>121641539</v>
       </c>
       <c r="B5" t="n">
-        <v>98017</v>
+        <v>5173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220093</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429401</v>
+        <v>429471</v>
       </c>
       <c r="R5" t="n">
-        <v>6383436</v>
+        <v>6383434</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Anna Ljungqvist</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121641540</v>
       </c>
       <c r="B2" t="n">
-        <v>91133</v>
+        <v>91147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641538</v>
+        <v>121641537</v>
       </c>
       <c r="B3" t="n">
-        <v>98017</v>
+        <v>98035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429422</v>
+        <v>429401</v>
       </c>
       <c r="R3" t="n">
-        <v>6383435</v>
+        <v>6383436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641537</v>
+        <v>121641538</v>
       </c>
       <c r="B4" t="n">
-        <v>98017</v>
+        <v>98035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429401</v>
+        <v>429422</v>
       </c>
       <c r="R4" t="n">
-        <v>6383436</v>
+        <v>6383435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121641540</v>
+        <v>121641537</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>98037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220093</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429450</v>
+        <v>429401</v>
       </c>
       <c r="R2" t="n">
-        <v>6383433</v>
+        <v>6383436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Nina Marliden</t>
+          <t>Ellen Hultman, Anna Ljungqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121641537</v>
+        <v>121641538</v>
       </c>
       <c r="B3" t="n">
-        <v>98035</v>
+        <v>98037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>429401</v>
+        <v>429422</v>
       </c>
       <c r="R3" t="n">
-        <v>6383436</v>
+        <v>6383435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641538</v>
+        <v>121641540</v>
       </c>
       <c r="B4" t="n">
-        <v>98035</v>
+        <v>91149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429422</v>
+        <v>429450</v>
       </c>
       <c r="R4" t="n">
-        <v>6383435</v>
+        <v>6383433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellen Hultman, Anna Ljungqvist</t>
+          <t>Ellen Hultman, Nina Marliden</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 63489-2020 artfynd.xlsx
+++ b/artfynd/A 63489-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121641537</v>
       </c>
       <c r="B2" t="n">
-        <v>98037</v>
+        <v>98044</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121641538</v>
       </c>
       <c r="B3" t="n">
-        <v>98037</v>
+        <v>98044</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121641540</v>
+        <v>121641539</v>
       </c>
       <c r="B4" t="n">
-        <v>91149</v>
+        <v>5173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>429450</v>
+        <v>429471</v>
       </c>
       <c r="R4" t="n">
-        <v>6383433</v>
+        <v>6383434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121641539</v>
+        <v>121641540</v>
       </c>
       <c r="B5" t="n">
-        <v>5173</v>
+        <v>91150</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>429471</v>
+        <v>429450</v>
       </c>
       <c r="R5" t="n">
-        <v>6383434</v>
+        <v>6383433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
